--- a/data/price.xlsx
+++ b/data/price.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Лес Проф База\Бот\pythonProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Лес Проф База\Создание сайта пиломатериалов\Прайс\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39480C8-5CE2-41BB-9DD6-C69A98AC3D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B5BDD4-BCA7-4F38-85E5-9440D450EA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="229">
   <si>
     <t>№</t>
   </si>
@@ -191,21 +191,12 @@
     <t>7. НАЛИЧНИК</t>
   </si>
   <si>
-    <t>90 × 2.2 м (3 м)</t>
-  </si>
-  <si>
     <t>300 (350) ₽ / шт.</t>
   </si>
   <si>
-    <t>120 × 2.2 м (3 м)</t>
-  </si>
-  <si>
     <t>350 (400) ₽ / шт.</t>
   </si>
   <si>
-    <t>140 × 2.2 м (3 м)</t>
-  </si>
-  <si>
     <t>400 (450) ₽ / шт.</t>
   </si>
   <si>
@@ -320,9 +311,6 @@
     <t>13. БЛОК-ХАУС</t>
   </si>
   <si>
-    <t>14. ПЛАНКЕН</t>
-  </si>
-  <si>
     <t>15. ДОСКА ОБРЕЗНАЯ (ТУ / ГОСТ)</t>
   </si>
   <si>
@@ -449,9 +437,6 @@
     <t>110, 135</t>
   </si>
   <si>
-    <t>Планкен лиственница прямой / скош.</t>
-  </si>
-  <si>
     <t>90, 95</t>
   </si>
   <si>
@@ -503,12 +488,6 @@
     <t>110 (120)</t>
   </si>
   <si>
-    <t>5. ПОЛУВАЛИК</t>
-  </si>
-  <si>
-    <t>15 на 70 × 2.2 м (3 м)</t>
-  </si>
-  <si>
     <t>55 000 ₽ / м³</t>
   </si>
   <si>
@@ -569,9 +548,6 @@
     <t>Европлинтус (№ 21 - 22)</t>
   </si>
   <si>
-    <t>Штапик (№ 33)</t>
-  </si>
-  <si>
     <t>Сучковые (№ 42 - 53)</t>
   </si>
   <si>
@@ -587,9 +563,6 @@
     <t>Евровагонка (№ 61)</t>
   </si>
   <si>
-    <t>Косой планкен (№ 90)</t>
-  </si>
-  <si>
     <t>Камерная сушка (№ 91 - 92)</t>
   </si>
   <si>
@@ -701,7 +674,46 @@
     <t>65 × 3</t>
   </si>
   <si>
-    <t>OSB плита</t>
+    <t>Без сучковые (№ 54 - 56)</t>
+  </si>
+  <si>
+    <t>15 × 70 × 2.2 м (3 м)</t>
+  </si>
+  <si>
+    <t>15 × 90 × 2.2 м (3 м)</t>
+  </si>
+  <si>
+    <t>15 × 120 × 2.2 м (3 м)</t>
+  </si>
+  <si>
+    <t>15 × 140 × 2.2 м (3 м)</t>
+  </si>
+  <si>
+    <t>5. ШТАПИК</t>
+  </si>
+  <si>
+    <t>6 м</t>
+  </si>
+  <si>
+    <t>85 000 ₽ / м³</t>
+  </si>
+  <si>
+    <t>Клееный брус из лиственницы</t>
+  </si>
+  <si>
+    <t>Сорт 1</t>
+  </si>
+  <si>
+    <t>ОСП (OSB-3) плита</t>
+  </si>
+  <si>
+    <t>Планкен скошенный (№ 90)</t>
+  </si>
+  <si>
+    <t>14. ПЛАНКЕН ПРЯМОЙ</t>
+  </si>
+  <si>
+    <t>Планкен прямой и скошенный лиственница</t>
   </si>
 </sst>
 </file>
@@ -711,12 +723,20 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;₽&quot;;[Red]\-#,##0\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -935,7 +955,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1177,281 +1197,331 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1462,8 +1532,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF9897E2"/>
       <color rgb="FFFF0F0F"/>
-      <color rgb="FF9897E2"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1767,2016 +1837,2016 @@
   </cols>
   <sheetData>
     <row r="5" spans="6:11" ht="17.5">
-      <c r="F5" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="F5" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
     </row>
     <row r="6" spans="6:11" ht="15">
       <c r="F6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="54" t="s">
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="54"/>
+      <c r="K6" s="55"/>
     </row>
     <row r="7" spans="6:11" ht="15">
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" spans="6:11">
       <c r="F8" s="2">
         <v>1</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="55" t="s">
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="55"/>
+      <c r="K8" s="56"/>
     </row>
     <row r="9" spans="6:11" ht="15">
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
     </row>
     <row r="10" spans="6:11" ht="15">
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="27"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" spans="6:11" ht="15">
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
     </row>
     <row r="12" spans="6:11">
       <c r="F12" s="2">
         <v>2</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="22" t="s">
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="13" spans="6:11">
       <c r="F13" s="2">
         <v>3</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="22" t="s">
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="22"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" spans="6:11">
       <c r="F14" s="2">
         <v>4</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="22" t="s">
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="22"/>
+      <c r="K14" s="23"/>
     </row>
     <row r="15" spans="6:11">
       <c r="F15" s="2">
         <v>5</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="22" t="s">
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="23"/>
     </row>
     <row r="16" spans="6:11">
       <c r="F16" s="2">
         <v>6</v>
       </c>
-      <c r="G16" s="23" t="s">
+      <c r="G16" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="22" t="s">
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="22"/>
+      <c r="K16" s="23"/>
     </row>
     <row r="17" spans="6:11">
       <c r="F17" s="2">
         <v>7</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="22" t="s">
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="22"/>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" spans="6:11" ht="15">
-      <c r="F18" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
+      <c r="F18" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
     </row>
     <row r="19" spans="6:11">
       <c r="F19" s="2">
         <v>8</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="22" t="s">
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="22"/>
+      <c r="K19" s="23"/>
     </row>
     <row r="20" spans="6:11">
       <c r="F20" s="2">
         <v>9</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="22" t="s">
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="22"/>
+      <c r="K20" s="23"/>
     </row>
     <row r="21" spans="6:11">
       <c r="F21" s="2">
         <v>10</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="22" t="s">
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="22"/>
+      <c r="K21" s="23"/>
     </row>
     <row r="22" spans="6:11">
       <c r="F22" s="2">
         <v>11</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="22" t="s">
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="K22" s="22"/>
+      <c r="K22" s="23"/>
     </row>
     <row r="23" spans="6:11">
       <c r="F23" s="2">
         <v>12</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K23" s="22"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="23"/>
     </row>
     <row r="24" spans="6:11">
       <c r="F24" s="2">
         <v>13</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="K24" s="22"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" s="23"/>
     </row>
     <row r="25" spans="6:11">
       <c r="F25" s="2">
         <v>14</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="K25" s="22"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="K25" s="23"/>
     </row>
     <row r="26" spans="6:11">
       <c r="F26" s="2">
         <v>15</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="K26" s="22"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="K26" s="23"/>
     </row>
     <row r="27" spans="6:11">
       <c r="F27" s="2">
         <v>16</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K27" s="22"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="K27" s="23"/>
     </row>
     <row r="28" spans="6:11" ht="15">
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
     </row>
     <row r="29" spans="6:11">
       <c r="F29" s="2">
         <v>17</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="22" t="s">
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="22"/>
+      <c r="K29" s="23"/>
     </row>
     <row r="30" spans="6:11">
       <c r="F30" s="2">
         <v>18</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K30" s="22"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="K30" s="23"/>
     </row>
     <row r="31" spans="6:11">
       <c r="F31" s="2">
         <v>19</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K31" s="22"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="K31" s="23"/>
     </row>
     <row r="32" spans="6:11">
       <c r="F32" s="2">
         <v>20</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="22" t="s">
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="K32" s="22"/>
+      <c r="K32" s="23"/>
     </row>
     <row r="33" spans="6:11">
-      <c r="F33" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
+      <c r="F33" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
     </row>
     <row r="34" spans="6:11">
       <c r="F34" s="2">
         <v>21</v>
       </c>
-      <c r="G34" s="51" t="s">
+      <c r="G34" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="22" t="s">
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="K34" s="22"/>
+      <c r="K34" s="23"/>
     </row>
     <row r="35" spans="6:11">
       <c r="F35" s="2">
         <v>22</v>
       </c>
-      <c r="G35" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="K35" s="22"/>
+      <c r="G35" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="K35" s="23"/>
     </row>
     <row r="36" spans="6:11" ht="15">
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
     </row>
     <row r="37" spans="6:11">
       <c r="F37" s="2">
         <v>23</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="G37" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="22" t="s">
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="K37" s="22"/>
+      <c r="K37" s="23"/>
     </row>
     <row r="38" spans="6:11">
       <c r="F38" s="2">
         <v>24</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="G38" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="K38" s="22"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="K38" s="23"/>
     </row>
     <row r="39" spans="6:11">
       <c r="F39" s="2">
         <v>25</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K39" s="22"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="K39" s="23"/>
     </row>
     <row r="40" spans="6:11">
       <c r="F40" s="2">
         <v>26</v>
       </c>
-      <c r="G40" s="23" t="s">
+      <c r="G40" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="22" t="s">
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="K40" s="22"/>
+      <c r="K40" s="23"/>
     </row>
     <row r="41" spans="6:11">
       <c r="F41" s="2">
         <v>27</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K41" s="22"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="K41" s="23"/>
     </row>
     <row r="42" spans="6:11">
       <c r="F42" s="2">
         <v>28</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="K42" s="22"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="K42" s="23"/>
     </row>
     <row r="43" spans="6:11">
       <c r="F43" s="2">
         <v>29</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="K43" s="22"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="K43" s="23"/>
     </row>
     <row r="44" spans="6:11">
       <c r="F44" s="2">
         <v>30</v>
       </c>
-      <c r="G44" s="23" t="s">
+      <c r="G44" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="K44" s="22"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="K44" s="23"/>
     </row>
     <row r="45" spans="6:11" ht="15">
-      <c r="F45" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="24"/>
-      <c r="K45" s="24"/>
+      <c r="F45" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="27"/>
+      <c r="J45" s="27"/>
+      <c r="K45" s="27"/>
     </row>
     <row r="46" spans="6:11">
       <c r="F46" s="2">
         <v>31</v>
       </c>
-      <c r="G46" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K46" s="22"/>
+      <c r="G46" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="23"/>
     </row>
     <row r="47" spans="6:11">
       <c r="F47" s="2">
         <v>32</v>
       </c>
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="23"/>
+    </row>
+    <row r="48" spans="6:11">
+      <c r="F48" s="2">
+        <v>33</v>
+      </c>
+      <c r="G48" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="K47" s="22"/>
-    </row>
-    <row r="48" spans="6:11">
-      <c r="F48" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-    </row>
-    <row r="49" spans="5:12">
-      <c r="F49" s="2">
-        <v>33</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="K49" s="22"/>
-    </row>
-    <row r="50" spans="5:12" ht="15">
-      <c r="F50" s="24" t="s">
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="K48" s="23"/>
+    </row>
+    <row r="49" spans="5:12" ht="15">
+      <c r="F49" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="27"/>
+    </row>
+    <row r="50" spans="5:12">
+      <c r="F50" s="2">
+        <v>34</v>
+      </c>
+      <c r="G50" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="23"/>
     </row>
     <row r="51" spans="5:12">
       <c r="F51" s="2">
-        <v>34</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="H51" s="51"/>
-      <c r="I51" s="51"/>
-      <c r="J51" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K51" s="22"/>
+        <v>35</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="K51" s="23"/>
     </row>
     <row r="52" spans="5:12">
       <c r="F52" s="2">
-        <v>35</v>
-      </c>
-      <c r="G52" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="K52" s="22"/>
+        <v>36</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" s="23"/>
     </row>
     <row r="53" spans="5:12">
       <c r="F53" s="2">
-        <v>36</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="K53" s="22"/>
-    </row>
-    <row r="54" spans="5:12">
-      <c r="F54" s="2">
         <v>37</v>
       </c>
-      <c r="G54" s="51" t="s">
+      <c r="G53" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="H54" s="51"/>
-      <c r="I54" s="51"/>
-      <c r="J54" s="22" t="s">
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="K54" s="22"/>
-    </row>
-    <row r="55" spans="5:12" ht="15">
-      <c r="F55" s="24" t="s">
+      <c r="K53" s="23"/>
+    </row>
+    <row r="54" spans="5:12" ht="15">
+      <c r="F54" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="G55" s="24"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27"/>
+      <c r="K54" s="27"/>
+    </row>
+    <row r="55" spans="5:12">
+      <c r="F55" s="2">
+        <v>38</v>
+      </c>
+      <c r="G55" s="24" t="s">
+        <v>216</v>
+      </c>
       <c r="H55" s="24"/>
       <c r="I55" s="24"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="24"/>
+      <c r="J55" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K55" s="23"/>
+      <c r="L55" s="12"/>
     </row>
     <row r="56" spans="5:12">
       <c r="F56" s="2">
-        <v>38</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K56" s="22"/>
+      <c r="K56" s="23"/>
       <c r="L56" s="12"/>
     </row>
     <row r="57" spans="5:12">
       <c r="F57" s="2">
-        <v>39</v>
-      </c>
-      <c r="G57" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="K57" s="22"/>
+        <v>40</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K57" s="23"/>
       <c r="L57" s="12"/>
     </row>
     <row r="58" spans="5:12">
       <c r="F58" s="2">
-        <v>40</v>
-      </c>
-      <c r="G58" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="K58" s="22"/>
+        <v>41</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="K58" s="23"/>
       <c r="L58" s="12"/>
     </row>
-    <row r="59" spans="5:12">
-      <c r="F59" s="2">
-        <v>41</v>
-      </c>
-      <c r="G59" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="K59" s="22"/>
-      <c r="L59" s="12"/>
-    </row>
-    <row r="60" spans="5:12" ht="15">
-      <c r="F60" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="24"/>
-      <c r="K60" s="24"/>
+    <row r="59" spans="5:12" ht="15">
+      <c r="F59" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+    </row>
+    <row r="60" spans="5:12">
+      <c r="F60" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="G60" s="47"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="47"/>
+      <c r="J60" s="47"/>
+      <c r="K60" s="48"/>
     </row>
     <row r="61" spans="5:12">
-      <c r="F61" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="46"/>
-      <c r="K61" s="47"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="2">
+        <v>42</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="K61" s="23"/>
     </row>
     <row r="62" spans="5:12">
-      <c r="E62" s="12"/>
       <c r="F62" s="2">
-        <v>42</v>
-      </c>
-      <c r="G62" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="H62" s="23"/>
-      <c r="I62" s="23"/>
-      <c r="J62" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="K62" s="22"/>
+        <v>43</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="K62" s="23"/>
     </row>
     <row r="63" spans="5:12">
       <c r="F63" s="2">
-        <v>43</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="H63" s="23"/>
-      <c r="I63" s="23"/>
-      <c r="J63" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="K63" s="22"/>
+        <v>44</v>
+      </c>
+      <c r="G63" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="K63" s="23"/>
     </row>
     <row r="64" spans="5:12">
-      <c r="F64" s="2">
-        <v>44</v>
-      </c>
-      <c r="G64" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="K64" s="22"/>
+      <c r="F64" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="G64" s="50"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="50"/>
+      <c r="J64" s="50"/>
+      <c r="K64" s="51"/>
     </row>
     <row r="65" spans="6:11">
-      <c r="F65" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="G65" s="49"/>
-      <c r="H65" s="49"/>
-      <c r="I65" s="49"/>
-      <c r="J65" s="49"/>
-      <c r="K65" s="50"/>
+      <c r="F65" s="2">
+        <v>45</v>
+      </c>
+      <c r="G65" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="K65" s="23"/>
     </row>
     <row r="66" spans="6:11">
       <c r="F66" s="2">
-        <v>45</v>
-      </c>
-      <c r="G66" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="H66" s="23"/>
-      <c r="I66" s="23"/>
-      <c r="J66" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="K66" s="22"/>
+        <v>46</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="K66" s="23"/>
     </row>
     <row r="67" spans="6:11">
-      <c r="F67" s="2">
-        <v>46</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="K67" s="22"/>
+      <c r="F67" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="44"/>
+      <c r="J67" s="44"/>
+      <c r="K67" s="45"/>
     </row>
     <row r="68" spans="6:11">
-      <c r="F68" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="G68" s="43"/>
-      <c r="H68" s="43"/>
-      <c r="I68" s="43"/>
-      <c r="J68" s="43"/>
-      <c r="K68" s="44"/>
+      <c r="F68" s="2">
+        <v>47</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K68" s="29"/>
     </row>
     <row r="69" spans="6:11">
       <c r="F69" s="2">
-        <v>47</v>
-      </c>
-      <c r="G69" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="H69" s="23"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="K69" s="28"/>
+        <v>48</v>
+      </c>
+      <c r="G69" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="31"/>
     </row>
     <row r="70" spans="6:11">
       <c r="F70" s="2">
-        <v>48</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="30"/>
+        <v>49</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H70" s="24"/>
+      <c r="I70" s="24"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="31"/>
     </row>
     <row r="71" spans="6:11">
       <c r="F71" s="2">
-        <v>49</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="30"/>
+        <v>50</v>
+      </c>
+      <c r="G71" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="H71" s="41"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="31"/>
     </row>
     <row r="72" spans="6:11">
       <c r="F72" s="2">
-        <v>50</v>
-      </c>
-      <c r="G72" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="H72" s="40"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="29"/>
-      <c r="K72" s="30"/>
+        <v>51</v>
+      </c>
+      <c r="G72" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="H72" s="41"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="31"/>
     </row>
     <row r="73" spans="6:11">
       <c r="F73" s="2">
-        <v>51</v>
-      </c>
-      <c r="G73" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="H73" s="40"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="29"/>
-      <c r="K73" s="30"/>
+        <v>52</v>
+      </c>
+      <c r="G73" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="H73" s="41"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="31"/>
     </row>
     <row r="74" spans="6:11">
       <c r="F74" s="2">
-        <v>52</v>
-      </c>
-      <c r="G74" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="H74" s="40"/>
-      <c r="I74" s="41"/>
-      <c r="J74" s="29"/>
-      <c r="K74" s="30"/>
+        <v>53</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="33"/>
     </row>
     <row r="75" spans="6:11">
-      <c r="F75" s="2">
-        <v>53</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="31"/>
-      <c r="K75" s="32"/>
+      <c r="F75" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="G75" s="47"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="47"/>
+      <c r="J75" s="47"/>
+      <c r="K75" s="48"/>
     </row>
     <row r="76" spans="6:11">
-      <c r="F76" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="G76" s="25"/>
-      <c r="H76" s="25"/>
-      <c r="I76" s="25"/>
-      <c r="J76" s="25"/>
-      <c r="K76" s="25"/>
+      <c r="F76" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="45"/>
     </row>
     <row r="77" spans="6:11">
       <c r="F77" s="2">
         <v>54</v>
       </c>
-      <c r="G77" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="K77" s="22"/>
+      <c r="G77" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="K77" s="23"/>
     </row>
     <row r="78" spans="6:11">
-      <c r="F78" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25"/>
-      <c r="I78" s="25"/>
-      <c r="J78" s="25"/>
-      <c r="K78" s="25"/>
+      <c r="F78" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
     </row>
     <row r="79" spans="6:11">
       <c r="F79" s="2">
         <v>55</v>
       </c>
-      <c r="G79" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K79" s="22"/>
+      <c r="G79" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H79" s="24"/>
+      <c r="I79" s="24"/>
+      <c r="J79" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="K79" s="23"/>
     </row>
     <row r="80" spans="6:11">
-      <c r="F80" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-      <c r="J80" s="25"/>
-      <c r="K80" s="25"/>
+      <c r="F80" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
     </row>
     <row r="81" spans="6:11">
       <c r="F81" s="2">
         <v>56</v>
       </c>
-      <c r="G81" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="H81" s="23"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="K81" s="22"/>
+      <c r="G81" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="H81" s="24"/>
+      <c r="I81" s="24"/>
+      <c r="J81" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="K81" s="23"/>
     </row>
     <row r="82" spans="6:11" ht="15">
-      <c r="F82" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="G82" s="24"/>
-      <c r="H82" s="24"/>
-      <c r="I82" s="24"/>
-      <c r="J82" s="24"/>
-      <c r="K82" s="24"/>
+      <c r="F82" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="27"/>
+      <c r="K82" s="27"/>
     </row>
     <row r="83" spans="6:11">
       <c r="F83" s="2">
         <v>57</v>
       </c>
-      <c r="G83" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H83" s="23"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="K83" s="22"/>
+      <c r="G83" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H83" s="24"/>
+      <c r="I83" s="24"/>
+      <c r="J83" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="K83" s="23"/>
     </row>
     <row r="84" spans="6:11">
       <c r="F84" s="2">
         <v>58</v>
       </c>
-      <c r="G84" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="H84" s="23"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="K84" s="22"/>
+      <c r="G84" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H84" s="24"/>
+      <c r="I84" s="24"/>
+      <c r="J84" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="K84" s="23"/>
     </row>
     <row r="85" spans="6:11">
       <c r="F85" s="2">
         <v>59</v>
       </c>
-      <c r="G85" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H85" s="51"/>
-      <c r="I85" s="51"/>
-      <c r="J85" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="K85" s="22"/>
+      <c r="G85" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="K85" s="23"/>
     </row>
     <row r="86" spans="6:11" ht="14" customHeight="1">
       <c r="F86" s="2">
         <v>60</v>
       </c>
-      <c r="G86" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="H86" s="51"/>
-      <c r="I86" s="51"/>
-      <c r="J86" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="K86" s="22"/>
+      <c r="G86" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H86" s="25"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="K86" s="23"/>
     </row>
     <row r="87" spans="6:11">
-      <c r="F87" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="G87" s="25"/>
-      <c r="H87" s="25"/>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25"/>
+      <c r="F87" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="26"/>
+      <c r="K87" s="26"/>
     </row>
     <row r="88" spans="6:11">
       <c r="F88" s="2">
         <v>61</v>
       </c>
-      <c r="G88" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="K88" s="22"/>
+      <c r="G88" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H88" s="24"/>
+      <c r="I88" s="24"/>
+      <c r="J88" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="K88" s="23"/>
     </row>
     <row r="89" spans="6:11" ht="15">
-      <c r="F89" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="G89" s="24"/>
-      <c r="H89" s="24"/>
-      <c r="I89" s="24"/>
-      <c r="J89" s="24"/>
-      <c r="K89" s="24"/>
+      <c r="F89" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G89" s="27"/>
+      <c r="H89" s="27"/>
+      <c r="I89" s="27"/>
+      <c r="J89" s="27"/>
+      <c r="K89" s="27"/>
     </row>
     <row r="90" spans="6:11">
       <c r="F90" s="2">
         <v>62</v>
       </c>
-      <c r="G90" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H90" s="23"/>
-      <c r="I90" s="23"/>
-      <c r="J90" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="K90" s="22"/>
+      <c r="G90" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H90" s="24"/>
+      <c r="I90" s="24"/>
+      <c r="J90" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="K90" s="23"/>
     </row>
     <row r="91" spans="6:11">
       <c r="F91" s="2">
         <v>63</v>
       </c>
-      <c r="G91" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="H91" s="23"/>
-      <c r="I91" s="23"/>
-      <c r="J91" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="K91" s="22"/>
+      <c r="G91" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H91" s="24"/>
+      <c r="I91" s="24"/>
+      <c r="J91" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="K91" s="23"/>
     </row>
     <row r="92" spans="6:11">
       <c r="F92" s="2">
         <v>64</v>
       </c>
-      <c r="G92" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H92" s="23"/>
-      <c r="I92" s="23"/>
-      <c r="J92" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="K92" s="22"/>
+      <c r="G92" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H92" s="24"/>
+      <c r="I92" s="24"/>
+      <c r="J92" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="K92" s="23"/>
     </row>
     <row r="93" spans="6:11" ht="15">
-      <c r="F93" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="G93" s="24"/>
-      <c r="H93" s="24"/>
-      <c r="I93" s="24"/>
-      <c r="J93" s="24"/>
-      <c r="K93" s="24"/>
+      <c r="F93" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G93" s="27"/>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27"/>
+      <c r="J93" s="27"/>
+      <c r="K93" s="27"/>
     </row>
     <row r="94" spans="6:11">
       <c r="F94" s="2">
         <v>65</v>
       </c>
-      <c r="G94" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="H94" s="23"/>
-      <c r="I94" s="23"/>
-      <c r="J94" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="K94" s="22"/>
+      <c r="G94" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="K94" s="23"/>
     </row>
     <row r="95" spans="6:11">
       <c r="F95" s="2">
         <v>66</v>
       </c>
-      <c r="G95" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="H95" s="23"/>
-      <c r="I95" s="23"/>
-      <c r="J95" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="K95" s="22"/>
+      <c r="G95" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="H95" s="24"/>
+      <c r="I95" s="24"/>
+      <c r="J95" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="K95" s="23"/>
     </row>
     <row r="96" spans="6:11">
       <c r="F96" s="2">
         <v>67</v>
       </c>
-      <c r="G96" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H96" s="23"/>
-      <c r="I96" s="23"/>
-      <c r="J96" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="K96" s="22"/>
+      <c r="G96" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H96" s="24"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="K96" s="23"/>
     </row>
     <row r="97" spans="6:12" ht="15">
-      <c r="F97" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="G97" s="24"/>
-      <c r="H97" s="24"/>
-      <c r="I97" s="24"/>
-      <c r="J97" s="24"/>
-      <c r="K97" s="24"/>
+      <c r="F97" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G97" s="27"/>
+      <c r="H97" s="27"/>
+      <c r="I97" s="27"/>
+      <c r="J97" s="27"/>
+      <c r="K97" s="27"/>
     </row>
     <row r="98" spans="6:12" ht="15" customHeight="1">
-      <c r="F98" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="G98" s="20"/>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
-      <c r="J98" s="20"/>
-      <c r="K98" s="21"/>
+      <c r="F98" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="21"/>
+      <c r="J98" s="21"/>
+      <c r="K98" s="22"/>
     </row>
     <row r="99" spans="6:12">
       <c r="F99" s="2">
         <v>68</v>
       </c>
-      <c r="G99" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="H99" s="23"/>
-      <c r="I99" s="23"/>
-      <c r="J99" s="22" t="s">
+      <c r="G99" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="H99" s="24"/>
+      <c r="I99" s="24"/>
+      <c r="J99" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K99" s="22"/>
+      <c r="K99" s="23"/>
     </row>
     <row r="100" spans="6:12">
       <c r="F100" s="2">
         <v>69</v>
       </c>
-      <c r="G100" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H100" s="23"/>
-      <c r="I100" s="23"/>
-      <c r="J100" s="22" t="s">
+      <c r="G100" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H100" s="24"/>
+      <c r="I100" s="24"/>
+      <c r="J100" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="K100" s="22"/>
+      <c r="K100" s="23"/>
     </row>
     <row r="101" spans="6:12">
       <c r="F101" s="2">
         <v>70</v>
       </c>
-      <c r="G101" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="H101" s="23"/>
-      <c r="I101" s="23"/>
-      <c r="J101" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="K101" s="22"/>
+      <c r="G101" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H101" s="24"/>
+      <c r="I101" s="24"/>
+      <c r="J101" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="K101" s="23"/>
     </row>
     <row r="102" spans="6:12">
       <c r="F102" s="2">
         <v>71</v>
       </c>
-      <c r="G102" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H102" s="23"/>
-      <c r="I102" s="23"/>
-      <c r="J102" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="K102" s="22"/>
+      <c r="G102" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
+      <c r="J102" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="K102" s="23"/>
     </row>
     <row r="103" spans="6:12">
       <c r="F103" s="2">
         <v>72</v>
       </c>
-      <c r="G103" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="H103" s="40"/>
-      <c r="I103" s="41"/>
-      <c r="J103" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="K103" s="22"/>
+      <c r="G103" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="H103" s="41"/>
+      <c r="I103" s="42"/>
+      <c r="J103" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="K103" s="23"/>
     </row>
     <row r="104" spans="6:12">
       <c r="F104" s="2">
         <v>73</v>
       </c>
-      <c r="G104" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="H104" s="40"/>
-      <c r="I104" s="41"/>
-      <c r="J104" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="K104" s="22"/>
+      <c r="G104" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="H104" s="41"/>
+      <c r="I104" s="42"/>
+      <c r="J104" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="K104" s="23"/>
     </row>
     <row r="105" spans="6:12">
       <c r="F105" s="2">
         <v>74</v>
       </c>
-      <c r="G105" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="H105" s="40"/>
-      <c r="I105" s="41"/>
-      <c r="J105" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="K105" s="22"/>
+      <c r="G105" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="H105" s="41"/>
+      <c r="I105" s="42"/>
+      <c r="J105" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="K105" s="23"/>
     </row>
     <row r="106" spans="6:12">
       <c r="F106" s="2">
         <v>75</v>
       </c>
-      <c r="G106" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="H106" s="40"/>
-      <c r="I106" s="41"/>
-      <c r="J106" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="K106" s="22"/>
+      <c r="G106" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="H106" s="41"/>
+      <c r="I106" s="42"/>
+      <c r="J106" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="K106" s="23"/>
     </row>
     <row r="107" spans="6:12">
       <c r="F107" s="2">
         <v>76</v>
       </c>
-      <c r="G107" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="H107" s="40"/>
-      <c r="I107" s="41"/>
-      <c r="J107" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="K107" s="22"/>
+      <c r="G107" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="H107" s="41"/>
+      <c r="I107" s="42"/>
+      <c r="J107" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="K107" s="23"/>
     </row>
     <row r="108" spans="6:12">
       <c r="F108" s="2">
         <v>77</v>
       </c>
-      <c r="G108" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="H108" s="40"/>
-      <c r="I108" s="41"/>
-      <c r="J108" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="K108" s="22"/>
+      <c r="G108" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="H108" s="41"/>
+      <c r="I108" s="42"/>
+      <c r="J108" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="K108" s="23"/>
       <c r="L108" s="13"/>
     </row>
     <row r="109" spans="6:12">
       <c r="F109" s="2">
         <v>78</v>
       </c>
-      <c r="G109" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="H109" s="40"/>
-      <c r="I109" s="41"/>
-      <c r="J109" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="K109" s="22"/>
+      <c r="G109" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="H109" s="41"/>
+      <c r="I109" s="42"/>
+      <c r="J109" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="K109" s="23"/>
     </row>
     <row r="110" spans="6:12">
       <c r="F110" s="2">
         <v>79</v>
       </c>
-      <c r="G110" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="H110" s="40"/>
-      <c r="I110" s="41"/>
-      <c r="J110" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="K110" s="22"/>
+      <c r="G110" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="H110" s="41"/>
+      <c r="I110" s="42"/>
+      <c r="J110" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="K110" s="23"/>
     </row>
     <row r="111" spans="6:12">
       <c r="F111" s="2">
         <v>80</v>
       </c>
-      <c r="G111" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H111" s="40"/>
-      <c r="I111" s="41"/>
-      <c r="J111" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="K111" s="22"/>
+      <c r="G111" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="H111" s="41"/>
+      <c r="I111" s="42"/>
+      <c r="J111" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="K111" s="23"/>
     </row>
     <row r="112" spans="6:12">
       <c r="F112" s="2">
         <v>81</v>
       </c>
-      <c r="G112" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="H112" s="40"/>
-      <c r="I112" s="41"/>
-      <c r="J112" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="K112" s="22"/>
+      <c r="G112" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H112" s="41"/>
+      <c r="I112" s="42"/>
+      <c r="J112" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="K112" s="23"/>
     </row>
     <row r="113" spans="6:11">
       <c r="F113" s="2">
         <v>82</v>
       </c>
-      <c r="G113" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="H113" s="40"/>
-      <c r="I113" s="41"/>
-      <c r="J113" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="K113" s="22"/>
+      <c r="G113" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="H113" s="41"/>
+      <c r="I113" s="42"/>
+      <c r="J113" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="K113" s="23"/>
     </row>
     <row r="114" spans="6:11" ht="15">
-      <c r="F114" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="G114" s="24"/>
-      <c r="H114" s="24"/>
-      <c r="I114" s="24"/>
-      <c r="J114" s="24"/>
-      <c r="K114" s="24"/>
+      <c r="F114" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G114" s="27"/>
+      <c r="H114" s="27"/>
+      <c r="I114" s="27"/>
+      <c r="J114" s="27"/>
+      <c r="K114" s="27"/>
     </row>
     <row r="115" spans="6:11" ht="15">
       <c r="F115" s="2">
         <v>83</v>
       </c>
-      <c r="G115" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="H115" s="23"/>
-      <c r="I115" s="23"/>
-      <c r="J115" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="K115" s="38"/>
+      <c r="G115" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
+      <c r="J115" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="K115" s="39"/>
     </row>
     <row r="116" spans="6:11" ht="15">
       <c r="F116" s="2">
         <v>84</v>
       </c>
-      <c r="G116" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H116" s="23"/>
-      <c r="I116" s="23"/>
-      <c r="J116" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="K116" s="38"/>
+      <c r="G116" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H116" s="24"/>
+      <c r="I116" s="24"/>
+      <c r="J116" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="K116" s="39"/>
     </row>
     <row r="117" spans="6:11" ht="15">
       <c r="F117" s="2">
         <v>85</v>
       </c>
-      <c r="G117" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="H117" s="23"/>
-      <c r="I117" s="23"/>
-      <c r="J117" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="K117" s="38"/>
+      <c r="G117" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H117" s="24"/>
+      <c r="I117" s="24"/>
+      <c r="J117" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="K117" s="39"/>
     </row>
     <row r="118" spans="6:11" ht="15">
-      <c r="F118" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="G118" s="24"/>
-      <c r="H118" s="24"/>
-      <c r="I118" s="24"/>
-      <c r="J118" s="24"/>
-      <c r="K118" s="24"/>
+      <c r="F118" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="G118" s="27"/>
+      <c r="H118" s="27"/>
+      <c r="I118" s="27"/>
+      <c r="J118" s="27"/>
+      <c r="K118" s="27"/>
     </row>
     <row r="119" spans="6:11">
       <c r="F119" s="2">
         <v>86</v>
       </c>
-      <c r="G119" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="H119" s="23"/>
-      <c r="I119" s="23"/>
-      <c r="J119" s="22" t="s">
+      <c r="G119" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H119" s="24"/>
+      <c r="I119" s="24"/>
+      <c r="J119" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="K119" s="22"/>
+      <c r="K119" s="23"/>
     </row>
     <row r="120" spans="6:11">
       <c r="F120" s="2">
         <v>87</v>
       </c>
-      <c r="G120" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="H120" s="23"/>
-      <c r="I120" s="23"/>
-      <c r="J120" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="K120" s="22"/>
+      <c r="G120" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H120" s="24"/>
+      <c r="I120" s="24"/>
+      <c r="J120" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="K120" s="23"/>
     </row>
     <row r="121" spans="6:11">
       <c r="F121" s="2">
         <v>88</v>
       </c>
-      <c r="G121" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="H121" s="23"/>
-      <c r="I121" s="23"/>
-      <c r="J121" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="K121" s="22"/>
+      <c r="G121" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
+      <c r="J121" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="K121" s="23"/>
     </row>
     <row r="122" spans="6:11">
       <c r="F122" s="2">
         <v>89</v>
       </c>
-      <c r="G122" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H122" s="23"/>
-      <c r="I122" s="23"/>
-      <c r="J122" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="K122" s="22"/>
+      <c r="G122" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="H122" s="24"/>
+      <c r="I122" s="24"/>
+      <c r="J122" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="K122" s="23"/>
     </row>
     <row r="123" spans="6:11">
-      <c r="F123" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="G123" s="25"/>
-      <c r="H123" s="25"/>
-      <c r="I123" s="25"/>
-      <c r="J123" s="25"/>
-      <c r="K123" s="25"/>
+      <c r="F123" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="G123" s="26"/>
+      <c r="H123" s="26"/>
+      <c r="I123" s="26"/>
+      <c r="J123" s="26"/>
+      <c r="K123" s="26"/>
     </row>
     <row r="124" spans="6:11">
       <c r="F124" s="2">
         <v>90</v>
       </c>
-      <c r="G124" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="H124" s="23"/>
-      <c r="I124" s="23"/>
-      <c r="J124" s="22" t="s">
+      <c r="G124" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="K124" s="23"/>
+    </row>
+    <row r="125" spans="6:11" ht="15">
+      <c r="F125" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G125" s="27"/>
+      <c r="H125" s="27"/>
+      <c r="I125" s="27"/>
+      <c r="J125" s="27"/>
+      <c r="K125" s="27"/>
+    </row>
+    <row r="126" spans="6:11">
+      <c r="F126" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="K124" s="22"/>
-    </row>
-    <row r="125" spans="6:11" ht="15">
-      <c r="F125" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="G125" s="24"/>
-      <c r="H125" s="24"/>
-      <c r="I125" s="24"/>
-      <c r="J125" s="24"/>
-      <c r="K125" s="24"/>
-    </row>
-    <row r="126" spans="6:11">
-      <c r="F126" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="G126" s="33"/>
-      <c r="H126" s="33"/>
-      <c r="I126" s="33"/>
-      <c r="J126" s="33"/>
-      <c r="K126" s="33"/>
+      <c r="G126" s="34"/>
+      <c r="H126" s="34"/>
+      <c r="I126" s="34"/>
+      <c r="J126" s="34"/>
+      <c r="K126" s="34"/>
     </row>
     <row r="127" spans="6:11">
       <c r="F127" s="2">
         <v>91</v>
       </c>
-      <c r="G127" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="H127" s="23"/>
-      <c r="I127" s="23"/>
-      <c r="J127" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="K127" s="28"/>
+      <c r="G127" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
+      <c r="J127" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="K127" s="29"/>
     </row>
     <row r="128" spans="6:11">
       <c r="F128" s="2">
         <v>92</v>
       </c>
-      <c r="G128" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H128" s="23"/>
-      <c r="I128" s="23"/>
-      <c r="J128" s="31"/>
-      <c r="K128" s="32"/>
+      <c r="G128" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
+      <c r="J128" s="32"/>
+      <c r="K128" s="33"/>
     </row>
     <row r="129" spans="6:11" ht="15.5">
-      <c r="F129" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="G129" s="35"/>
-      <c r="H129" s="35"/>
-      <c r="I129" s="35"/>
-      <c r="J129" s="35"/>
-      <c r="K129" s="36"/>
+      <c r="F129" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="G129" s="36"/>
+      <c r="H129" s="36"/>
+      <c r="I129" s="36"/>
+      <c r="J129" s="36"/>
+      <c r="K129" s="37"/>
     </row>
     <row r="130" spans="6:11">
-      <c r="F130" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="G130" s="25"/>
-      <c r="H130" s="25"/>
-      <c r="I130" s="25"/>
-      <c r="J130" s="25"/>
-      <c r="K130" s="25"/>
+      <c r="F130" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="G130" s="26"/>
+      <c r="H130" s="26"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="26"/>
     </row>
     <row r="131" spans="6:11">
       <c r="F131" s="2">
         <v>93</v>
       </c>
-      <c r="G131" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="H131" s="23"/>
-      <c r="I131" s="23"/>
-      <c r="J131" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="K131" s="22"/>
+      <c r="G131" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="H131" s="24"/>
+      <c r="I131" s="24"/>
+      <c r="J131" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="K131" s="23"/>
     </row>
     <row r="132" spans="6:11">
       <c r="F132" s="2">
         <v>94</v>
       </c>
-      <c r="G132" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="H132" s="23"/>
-      <c r="I132" s="23"/>
-      <c r="J132" s="22"/>
-      <c r="K132" s="22"/>
+      <c r="G132" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="H132" s="24"/>
+      <c r="I132" s="24"/>
+      <c r="J132" s="23"/>
+      <c r="K132" s="23"/>
     </row>
     <row r="133" spans="6:11">
       <c r="F133" s="2">
         <v>95</v>
       </c>
-      <c r="G133" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H133" s="23"/>
-      <c r="I133" s="23"/>
-      <c r="J133" s="22"/>
-      <c r="K133" s="22"/>
+      <c r="G133" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="H133" s="24"/>
+      <c r="I133" s="24"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="23"/>
     </row>
     <row r="134" spans="6:11">
       <c r="F134" s="2">
         <v>96</v>
       </c>
-      <c r="G134" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="H134" s="23"/>
-      <c r="I134" s="23"/>
-      <c r="J134" s="22"/>
-      <c r="K134" s="22"/>
+      <c r="G134" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H134" s="24"/>
+      <c r="I134" s="24"/>
+      <c r="J134" s="23"/>
+      <c r="K134" s="23"/>
     </row>
     <row r="135" spans="6:11">
       <c r="F135" s="2">
         <v>97</v>
       </c>
-      <c r="G135" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H135" s="23"/>
-      <c r="I135" s="23"/>
-      <c r="J135" s="22"/>
-      <c r="K135" s="22"/>
+      <c r="G135" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H135" s="24"/>
+      <c r="I135" s="24"/>
+      <c r="J135" s="23"/>
+      <c r="K135" s="23"/>
     </row>
     <row r="136" spans="6:11">
       <c r="F136" s="2">
         <v>98</v>
       </c>
-      <c r="G136" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="H136" s="23"/>
-      <c r="I136" s="23"/>
-      <c r="J136" s="22"/>
-      <c r="K136" s="22"/>
+      <c r="G136" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H136" s="24"/>
+      <c r="I136" s="24"/>
+      <c r="J136" s="23"/>
+      <c r="K136" s="23"/>
     </row>
     <row r="137" spans="6:11">
       <c r="F137" s="2">
         <v>99</v>
       </c>
-      <c r="G137" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H137" s="23"/>
-      <c r="I137" s="23"/>
-      <c r="J137" s="22"/>
-      <c r="K137" s="22"/>
+      <c r="G137" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="H137" s="24"/>
+      <c r="I137" s="24"/>
+      <c r="J137" s="23"/>
+      <c r="K137" s="23"/>
     </row>
     <row r="138" spans="6:11">
       <c r="F138" s="2">
         <v>100</v>
       </c>
-      <c r="G138" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="H138" s="23"/>
-      <c r="I138" s="23"/>
-      <c r="J138" s="22"/>
-      <c r="K138" s="22"/>
+      <c r="G138" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="H138" s="24"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="23"/>
+      <c r="K138" s="23"/>
     </row>
     <row r="139" spans="6:11">
       <c r="F139" s="2">
         <v>101</v>
       </c>
-      <c r="G139" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="H139" s="23"/>
-      <c r="I139" s="23"/>
-      <c r="J139" s="22"/>
-      <c r="K139" s="22"/>
+      <c r="G139" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H139" s="24"/>
+      <c r="I139" s="24"/>
+      <c r="J139" s="23"/>
+      <c r="K139" s="23"/>
     </row>
     <row r="140" spans="6:11">
       <c r="F140" s="2">
         <v>102</v>
       </c>
-      <c r="G140" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="H140" s="23"/>
-      <c r="I140" s="23"/>
-      <c r="J140" s="22"/>
-      <c r="K140" s="22"/>
+      <c r="G140" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="H140" s="24"/>
+      <c r="I140" s="24"/>
+      <c r="J140" s="23"/>
+      <c r="K140" s="23"/>
     </row>
     <row r="141" spans="6:11">
       <c r="F141" s="2">
         <v>103</v>
       </c>
-      <c r="G141" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H141" s="23"/>
-      <c r="I141" s="23"/>
-      <c r="J141" s="22"/>
-      <c r="K141" s="22"/>
+      <c r="G141" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H141" s="24"/>
+      <c r="I141" s="24"/>
+      <c r="J141" s="23"/>
+      <c r="K141" s="23"/>
     </row>
     <row r="142" spans="6:11">
-      <c r="F142" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="G142" s="33"/>
-      <c r="H142" s="33"/>
-      <c r="I142" s="33"/>
-      <c r="J142" s="33"/>
-      <c r="K142" s="33"/>
+      <c r="F142" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="G142" s="34"/>
+      <c r="H142" s="34"/>
+      <c r="I142" s="34"/>
+      <c r="J142" s="34"/>
+      <c r="K142" s="34"/>
     </row>
     <row r="143" spans="6:11">
       <c r="F143" s="2">
         <v>104</v>
       </c>
-      <c r="G143" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="H143" s="23"/>
-      <c r="I143" s="23"/>
-      <c r="J143" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="K143" s="22"/>
+      <c r="G143" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="K143" s="23"/>
     </row>
     <row r="144" spans="6:11">
       <c r="F144" s="2">
         <v>105</v>
       </c>
-      <c r="G144" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="H144" s="23"/>
-      <c r="I144" s="23"/>
-      <c r="J144" s="22"/>
-      <c r="K144" s="22"/>
+      <c r="G144" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H144" s="24"/>
+      <c r="I144" s="24"/>
+      <c r="J144" s="23"/>
+      <c r="K144" s="23"/>
     </row>
     <row r="145" spans="6:11">
       <c r="F145" s="2">
         <v>106</v>
       </c>
-      <c r="G145" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H145" s="23"/>
-      <c r="I145" s="23"/>
-      <c r="J145" s="22"/>
-      <c r="K145" s="22"/>
+      <c r="G145" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H145" s="24"/>
+      <c r="I145" s="24"/>
+      <c r="J145" s="23"/>
+      <c r="K145" s="23"/>
     </row>
     <row r="146" spans="6:11">
       <c r="F146" s="2">
         <v>107</v>
       </c>
-      <c r="G146" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="H146" s="23"/>
-      <c r="I146" s="23"/>
-      <c r="J146" s="22"/>
-      <c r="K146" s="22"/>
+      <c r="G146" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H146" s="24"/>
+      <c r="I146" s="24"/>
+      <c r="J146" s="23"/>
+      <c r="K146" s="23"/>
     </row>
     <row r="147" spans="6:11">
       <c r="F147" s="2">
         <v>108</v>
       </c>
-      <c r="G147" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H147" s="23"/>
-      <c r="I147" s="23"/>
-      <c r="J147" s="22"/>
-      <c r="K147" s="22"/>
+      <c r="G147" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="H147" s="24"/>
+      <c r="I147" s="24"/>
+      <c r="J147" s="23"/>
+      <c r="K147" s="23"/>
     </row>
     <row r="148" spans="6:11">
       <c r="F148" s="2">
         <v>109</v>
       </c>
-      <c r="G148" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="H148" s="23"/>
-      <c r="I148" s="23"/>
-      <c r="J148" s="22"/>
-      <c r="K148" s="22"/>
+      <c r="G148" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H148" s="24"/>
+      <c r="I148" s="24"/>
+      <c r="J148" s="23"/>
+      <c r="K148" s="23"/>
     </row>
     <row r="149" spans="6:11">
       <c r="F149" s="2">
         <v>110</v>
       </c>
-      <c r="G149" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="H149" s="23"/>
-      <c r="I149" s="23"/>
-      <c r="J149" s="22"/>
-      <c r="K149" s="22"/>
+      <c r="G149" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H149" s="24"/>
+      <c r="I149" s="24"/>
+      <c r="J149" s="23"/>
+      <c r="K149" s="23"/>
     </row>
     <row r="150" spans="6:11">
       <c r="F150" s="2">
         <v>111</v>
       </c>
-      <c r="G150" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="H150" s="23"/>
-      <c r="I150" s="23"/>
-      <c r="J150" s="22"/>
-      <c r="K150" s="22"/>
+      <c r="G150" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H150" s="24"/>
+      <c r="I150" s="24"/>
+      <c r="J150" s="23"/>
+      <c r="K150" s="23"/>
     </row>
     <row r="151" spans="6:11">
       <c r="F151" s="2">
         <v>112</v>
       </c>
-      <c r="G151" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="H151" s="23"/>
-      <c r="I151" s="23"/>
-      <c r="J151" s="22"/>
-      <c r="K151" s="22"/>
+      <c r="G151" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="H151" s="24"/>
+      <c r="I151" s="24"/>
+      <c r="J151" s="23"/>
+      <c r="K151" s="23"/>
     </row>
     <row r="152" spans="6:11">
       <c r="F152" s="2">
         <v>113</v>
       </c>
-      <c r="G152" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="H152" s="23"/>
-      <c r="I152" s="23"/>
-      <c r="J152" s="22"/>
-      <c r="K152" s="22"/>
+      <c r="G152" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H152" s="24"/>
+      <c r="I152" s="24"/>
+      <c r="J152" s="23"/>
+      <c r="K152" s="23"/>
     </row>
     <row r="153" spans="6:11">
       <c r="F153" s="2">
         <v>114</v>
       </c>
-      <c r="G153" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="H153" s="23"/>
-      <c r="I153" s="23"/>
-      <c r="J153" s="22"/>
-      <c r="K153" s="22"/>
+      <c r="G153" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H153" s="24"/>
+      <c r="I153" s="24"/>
+      <c r="J153" s="23"/>
+      <c r="K153" s="23"/>
     </row>
     <row r="154" spans="6:11" ht="15.5">
-      <c r="F154" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="G154" s="35"/>
-      <c r="H154" s="35"/>
-      <c r="I154" s="35"/>
-      <c r="J154" s="35"/>
-      <c r="K154" s="36"/>
+      <c r="F154" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="G154" s="36"/>
+      <c r="H154" s="36"/>
+      <c r="I154" s="36"/>
+      <c r="J154" s="36"/>
+      <c r="K154" s="37"/>
     </row>
     <row r="155" spans="6:11">
       <c r="F155" s="2">
         <v>115</v>
       </c>
-      <c r="G155" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="H155" s="23"/>
-      <c r="I155" s="23"/>
-      <c r="J155" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="K155" s="28"/>
+      <c r="G155" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="H155" s="24"/>
+      <c r="I155" s="24"/>
+      <c r="J155" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="K155" s="29"/>
     </row>
     <row r="156" spans="6:11">
       <c r="F156" s="2">
         <v>116</v>
       </c>
-      <c r="G156" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="H156" s="23"/>
-      <c r="I156" s="23"/>
-      <c r="J156" s="31"/>
-      <c r="K156" s="32"/>
+      <c r="G156" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="H156" s="24"/>
+      <c r="I156" s="24"/>
+      <c r="J156" s="32"/>
+      <c r="K156" s="33"/>
     </row>
     <row r="157" spans="6:11">
       <c r="F157" s="2">
         <v>117</v>
       </c>
-      <c r="G157" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H157" s="23"/>
-      <c r="I157" s="23"/>
-      <c r="J157" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="K157" s="28"/>
+      <c r="G157" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="H157" s="24"/>
+      <c r="I157" s="24"/>
+      <c r="J157" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K157" s="29"/>
     </row>
     <row r="158" spans="6:11">
       <c r="F158" s="2">
         <v>118</v>
       </c>
-      <c r="G158" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="H158" s="23"/>
-      <c r="I158" s="23"/>
-      <c r="J158" s="29"/>
-      <c r="K158" s="30"/>
+      <c r="G158" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="H158" s="24"/>
+      <c r="I158" s="24"/>
+      <c r="J158" s="30"/>
+      <c r="K158" s="31"/>
     </row>
     <row r="159" spans="6:11">
       <c r="F159" s="2">
         <v>119</v>
       </c>
-      <c r="G159" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H159" s="23"/>
-      <c r="I159" s="23"/>
-      <c r="J159" s="29"/>
-      <c r="K159" s="30"/>
+      <c r="G159" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="H159" s="24"/>
+      <c r="I159" s="24"/>
+      <c r="J159" s="30"/>
+      <c r="K159" s="31"/>
     </row>
     <row r="160" spans="6:11">
       <c r="F160" s="2">
         <v>120</v>
       </c>
-      <c r="G160" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="H160" s="23"/>
-      <c r="I160" s="23"/>
-      <c r="J160" s="29"/>
-      <c r="K160" s="30"/>
+      <c r="G160" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H160" s="24"/>
+      <c r="I160" s="24"/>
+      <c r="J160" s="30"/>
+      <c r="K160" s="31"/>
     </row>
     <row r="161" spans="6:11">
       <c r="F161" s="2">
         <v>121</v>
       </c>
-      <c r="G161" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="H161" s="23"/>
-      <c r="I161" s="23"/>
-      <c r="J161" s="29"/>
-      <c r="K161" s="30"/>
+      <c r="G161" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="H161" s="24"/>
+      <c r="I161" s="24"/>
+      <c r="J161" s="30"/>
+      <c r="K161" s="31"/>
     </row>
     <row r="162" spans="6:11">
       <c r="F162" s="2">
         <v>122</v>
       </c>
-      <c r="G162" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="H162" s="23"/>
-      <c r="I162" s="23"/>
-      <c r="J162" s="31"/>
-      <c r="K162" s="32"/>
+      <c r="G162" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H162" s="24"/>
+      <c r="I162" s="24"/>
+      <c r="J162" s="32"/>
+      <c r="K162" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="248">
@@ -3885,52 +3955,51 @@
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="J44:K44"/>
     <mergeCell ref="F45:K45"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="J48:K48"/>
     <mergeCell ref="G46:I46"/>
     <mergeCell ref="J46:K46"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="F48:K48"/>
-    <mergeCell ref="F50:K50"/>
+    <mergeCell ref="F49:K49"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="J50:K50"/>
     <mergeCell ref="G51:I51"/>
     <mergeCell ref="J51:K51"/>
     <mergeCell ref="G52:I52"/>
     <mergeCell ref="J52:K52"/>
     <mergeCell ref="G53:I53"/>
     <mergeCell ref="J53:K53"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="F59:K59"/>
     <mergeCell ref="F60:K60"/>
-    <mergeCell ref="F61:K61"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="J64:K64"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="F55:K55"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="J65:K65"/>
+    <mergeCell ref="F54:K54"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="J55:K55"/>
     <mergeCell ref="G56:I56"/>
     <mergeCell ref="J56:K56"/>
     <mergeCell ref="G57:I57"/>
     <mergeCell ref="J57:K57"/>
     <mergeCell ref="G58:I58"/>
     <mergeCell ref="J58:K58"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="F65:K65"/>
-    <mergeCell ref="G67:I67"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="F68:K68"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="F64:K64"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="F67:K67"/>
+    <mergeCell ref="G68:I68"/>
     <mergeCell ref="G69:I69"/>
     <mergeCell ref="G70:I70"/>
     <mergeCell ref="G71:I71"/>
     <mergeCell ref="G72:I72"/>
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="G74:I74"/>
-    <mergeCell ref="G75:I75"/>
     <mergeCell ref="F76:K76"/>
     <mergeCell ref="G77:I77"/>
     <mergeCell ref="J77:K77"/>
@@ -3940,6 +4009,7 @@
     <mergeCell ref="F80:K80"/>
     <mergeCell ref="G81:I81"/>
     <mergeCell ref="J81:K81"/>
+    <mergeCell ref="F75:K75"/>
     <mergeCell ref="F82:K82"/>
     <mergeCell ref="G83:I83"/>
     <mergeCell ref="J83:K83"/>
@@ -3959,6 +4029,11 @@
     <mergeCell ref="J111:K111"/>
     <mergeCell ref="J112:K112"/>
     <mergeCell ref="J113:K113"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="J92:K92"/>
+    <mergeCell ref="F93:K93"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="J94:K94"/>
     <mergeCell ref="F118:K118"/>
     <mergeCell ref="G119:I119"/>
     <mergeCell ref="J119:K119"/>
@@ -3985,7 +4060,7 @@
     <mergeCell ref="G151:I151"/>
     <mergeCell ref="G152:I152"/>
     <mergeCell ref="G153:I153"/>
-    <mergeCell ref="J69:K75"/>
+    <mergeCell ref="J68:K74"/>
     <mergeCell ref="J131:K141"/>
     <mergeCell ref="J143:K153"/>
     <mergeCell ref="G84:I84"/>
@@ -4002,11 +4077,6 @@
     <mergeCell ref="G143:I143"/>
     <mergeCell ref="G144:I144"/>
     <mergeCell ref="G145:I145"/>
-    <mergeCell ref="G92:I92"/>
-    <mergeCell ref="J92:K92"/>
-    <mergeCell ref="F93:K93"/>
-    <mergeCell ref="G94:I94"/>
-    <mergeCell ref="J94:K94"/>
     <mergeCell ref="G95:I95"/>
     <mergeCell ref="J95:K95"/>
     <mergeCell ref="G86:I86"/>
@@ -4029,7 +4099,7 @@
     <mergeCell ref="J109:K109"/>
     <mergeCell ref="J110:K110"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="34" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -4040,7 +4110,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="C4:J66"/>
+  <dimension ref="C4:L79"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="16.36328125" customWidth="1"/>
@@ -4051,80 +4121,80 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:9" ht="17.5">
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="85" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+    </row>
+    <row r="5" spans="3:9" ht="15">
+      <c r="C5" s="84" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+    </row>
+    <row r="6" spans="3:9">
+      <c r="C6" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+    </row>
+    <row r="7" spans="3:9">
+      <c r="C7" s="80"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-    </row>
-    <row r="5" spans="3:9" ht="15">
-      <c r="C5" s="83" t="s">
+      <c r="F7" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-    </row>
-    <row r="6" spans="3:9">
-      <c r="C6" s="79" t="s">
+      <c r="G7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="H7" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-    </row>
-    <row r="7" spans="3:9">
-      <c r="C7" s="79"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F7" s="3" t="s">
+    </row>
+    <row r="8" spans="3:9">
+      <c r="C8" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="D8" s="76"/>
+      <c r="E8" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9">
-      <c r="C8" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="3:9">
@@ -4155,7 +4225,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E10" s="3">
         <v>2400</v>
@@ -4178,7 +4248,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E11" s="3">
         <v>2700</v>
@@ -4197,69 +4267,69 @@
       </c>
     </row>
     <row r="12" spans="3:9" ht="15">
-      <c r="C12" s="83" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
+      <c r="C12" s="84" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" spans="3:9">
-      <c r="C13" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
+      <c r="C13" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
     </row>
     <row r="14" spans="3:9">
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="81"/>
       <c r="E14" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9">
+      <c r="C15" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="15" spans="3:9">
-      <c r="C15" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="75"/>
+      <c r="D15" s="76"/>
       <c r="E15" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="3:9">
@@ -4378,69 +4448,69 @@
       </c>
     </row>
     <row r="21" spans="3:9" ht="15">
-      <c r="C21" s="83" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
+      <c r="C21" s="84" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="84"/>
     </row>
     <row r="22" spans="3:9">
-      <c r="C22" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
+      <c r="C22" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="83"/>
     </row>
     <row r="23" spans="3:9">
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="81"/>
       <c r="E23" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9">
+      <c r="C24" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="3:9">
-      <c r="C24" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="75"/>
+      <c r="D24" s="76"/>
       <c r="E24" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="3:9">
@@ -4471,7 +4541,7 @@
         <v>27</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E26" s="3">
         <v>3600</v>
@@ -4536,69 +4606,69 @@
       </c>
     </row>
     <row r="29" spans="3:9" ht="15">
-      <c r="C29" s="83" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
+      <c r="C29" s="94" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
     </row>
     <row r="30" spans="3:9">
-      <c r="C30" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82"/>
+      <c r="C30" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
     </row>
     <row r="31" spans="3:9">
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="81"/>
       <c r="E31" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9">
+      <c r="C32" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="3:9">
-      <c r="C32" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="75"/>
+      <c r="D32" s="76"/>
       <c r="E32" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="3:9">
@@ -4606,7 +4676,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E33" s="3">
         <v>2500</v>
@@ -4629,7 +4699,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E34" s="3">
         <v>2600</v>
@@ -4694,69 +4764,69 @@
       </c>
     </row>
     <row r="37" spans="3:9" ht="15">
-      <c r="C37" s="83" t="s">
-        <v>143</v>
-      </c>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
+      <c r="C37" s="84" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
     </row>
     <row r="38" spans="3:9">
-      <c r="C38" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="F38" s="82"/>
-      <c r="G38" s="82"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
+      <c r="C38" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E38" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="83"/>
+      <c r="I38" s="83"/>
     </row>
     <row r="39" spans="3:9">
-      <c r="C39" s="79"/>
-      <c r="D39" s="80"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="81"/>
       <c r="E39" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9">
+      <c r="C40" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="3:9">
-      <c r="C40" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" s="75"/>
+      <c r="D40" s="76"/>
       <c r="E40" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="3:9">
@@ -4806,69 +4876,69 @@
       </c>
     </row>
     <row r="43" spans="3:9" ht="15">
-      <c r="C43" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
+      <c r="C43" s="84" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
     </row>
     <row r="44" spans="3:9">
-      <c r="C44" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D44" s="80" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="F44" s="82"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
+      <c r="C44" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F44" s="83"/>
+      <c r="G44" s="83"/>
+      <c r="H44" s="83"/>
+      <c r="I44" s="83"/>
     </row>
     <row r="45" spans="3:9">
-      <c r="C45" s="79"/>
-      <c r="D45" s="80"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="81"/>
       <c r="E45" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9">
+      <c r="C46" s="75" t="s">
         <v>128</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="46" spans="3:9">
-      <c r="C46" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D46" s="75"/>
+      <c r="D46" s="76"/>
       <c r="E46" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="3:9">
@@ -4888,10 +4958,10 @@
         <v>1200</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="3:9">
@@ -4911,10 +4981,10 @@
         <v>1500</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49" spans="3:10">
@@ -4922,7 +4992,7 @@
         <v>14</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E49" s="3">
         <v>2600</v>
@@ -4934,124 +5004,124 @@
         <v>1600</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50" spans="3:10" ht="15">
-      <c r="C50" s="70" t="s">
-        <v>145</v>
-      </c>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
+      <c r="C50" s="71" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
     </row>
     <row r="51" spans="3:10">
       <c r="C51" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="G51" s="76" t="s">
-        <v>213</v>
-      </c>
-      <c r="H51" s="77"/>
-      <c r="I51" s="77"/>
+        <v>142</v>
+      </c>
+      <c r="G51" s="77" t="s">
+        <v>204</v>
+      </c>
+      <c r="H51" s="78"/>
+      <c r="I51" s="78"/>
     </row>
     <row r="52" spans="3:10">
-      <c r="C52" s="71"/>
-      <c r="D52" s="72"/>
-      <c r="E52" s="72"/>
-      <c r="F52" s="73"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="74"/>
       <c r="G52" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="H52" s="78" t="s">
-        <v>149</v>
-      </c>
-      <c r="I52" s="78"/>
+        <v>143</v>
+      </c>
+      <c r="H52" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="I52" s="79"/>
     </row>
     <row r="53" spans="3:10">
       <c r="C53" s="5">
         <v>40</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G53" s="7">
         <v>5000</v>
       </c>
-      <c r="H53" s="77" t="s">
-        <v>152</v>
-      </c>
-      <c r="I53" s="77"/>
+      <c r="H53" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="I53" s="78"/>
     </row>
     <row r="54" spans="3:10">
       <c r="C54" s="5">
         <v>18</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G54" s="7">
         <v>2600</v>
       </c>
-      <c r="H54" s="77" t="s">
-        <v>152</v>
-      </c>
-      <c r="I54" s="77"/>
+      <c r="H54" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="I54" s="78"/>
     </row>
     <row r="55" spans="3:10" ht="15" customHeight="1">
-      <c r="C55" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
+      <c r="C55" s="70" t="s">
+        <v>151</v>
+      </c>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
     </row>
     <row r="56" spans="3:10" ht="14.5" customHeight="1">
       <c r="C56" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F56" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="59"/>
+        <v>141</v>
+      </c>
+      <c r="F56" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="60"/>
       <c r="J56" s="15"/>
     </row>
     <row r="57" spans="3:10">
@@ -5064,12 +5134,12 @@
       <c r="E57" s="17">
         <v>6</v>
       </c>
-      <c r="F57" s="60" t="s">
-        <v>215</v>
-      </c>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="62"/>
+      <c r="F57" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="63"/>
     </row>
     <row r="58" spans="3:10">
       <c r="C58" s="16">
@@ -5081,10 +5151,10 @@
       <c r="E58" s="17">
         <v>6</v>
       </c>
-      <c r="F58" s="63"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="65"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="66"/>
     </row>
     <row r="59" spans="3:10">
       <c r="C59" s="16">
@@ -5096,10 +5166,10 @@
       <c r="E59" s="17">
         <v>6</v>
       </c>
-      <c r="F59" s="63"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="64"/>
-      <c r="I59" s="65"/>
+      <c r="F59" s="64"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="66"/>
     </row>
     <row r="60" spans="3:10">
       <c r="C60" s="16">
@@ -5111,10 +5181,10 @@
       <c r="E60" s="17">
         <v>6</v>
       </c>
-      <c r="F60" s="63"/>
-      <c r="G60" s="64"/>
-      <c r="H60" s="64"/>
-      <c r="I60" s="65"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65"/>
+      <c r="I60" s="66"/>
     </row>
     <row r="61" spans="3:10">
       <c r="C61" s="16">
@@ -5126,10 +5196,10 @@
       <c r="E61" s="17">
         <v>6</v>
       </c>
-      <c r="F61" s="63"/>
-      <c r="G61" s="64"/>
-      <c r="H61" s="64"/>
-      <c r="I61" s="65"/>
+      <c r="F61" s="64"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="66"/>
     </row>
     <row r="62" spans="3:10">
       <c r="C62" s="16">
@@ -5141,10 +5211,10 @@
       <c r="E62" s="17">
         <v>6</v>
       </c>
-      <c r="F62" s="63"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="64"/>
-      <c r="I62" s="65"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="65"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="66"/>
     </row>
     <row r="63" spans="3:10">
       <c r="C63" s="16">
@@ -5156,10 +5226,10 @@
       <c r="E63" s="17">
         <v>6</v>
       </c>
-      <c r="F63" s="63"/>
-      <c r="G63" s="64"/>
-      <c r="H63" s="64"/>
-      <c r="I63" s="65"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="65"/>
+      <c r="H63" s="65"/>
+      <c r="I63" s="66"/>
     </row>
     <row r="64" spans="3:10">
       <c r="C64" s="16">
@@ -5171,12 +5241,12 @@
       <c r="E64" s="17">
         <v>6</v>
       </c>
-      <c r="F64" s="63"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="64"/>
-      <c r="I64" s="65"/>
-    </row>
-    <row r="65" spans="3:9">
+      <c r="F64" s="64"/>
+      <c r="G64" s="65"/>
+      <c r="H64" s="65"/>
+      <c r="I64" s="66"/>
+    </row>
+    <row r="65" spans="3:12">
       <c r="C65" s="16">
         <v>150</v>
       </c>
@@ -5186,12 +5256,12 @@
       <c r="E65" s="17">
         <v>6</v>
       </c>
-      <c r="F65" s="63"/>
-      <c r="G65" s="64"/>
-      <c r="H65" s="64"/>
-      <c r="I65" s="65"/>
-    </row>
-    <row r="66" spans="3:9">
+      <c r="F65" s="64"/>
+      <c r="G65" s="65"/>
+      <c r="H65" s="65"/>
+      <c r="I65" s="66"/>
+    </row>
+    <row r="66" spans="3:12">
       <c r="C66" s="16">
         <v>200</v>
       </c>
@@ -5201,13 +5271,167 @@
       <c r="E66" s="17">
         <v>6</v>
       </c>
-      <c r="F66" s="66"/>
-      <c r="G66" s="67"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="68"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="68"/>
+      <c r="H66" s="68"/>
+      <c r="I66" s="69"/>
+    </row>
+    <row r="67" spans="3:12" ht="15">
+      <c r="C67" s="94" t="s">
+        <v>223</v>
+      </c>
+      <c r="D67" s="84"/>
+      <c r="E67" s="84"/>
+      <c r="F67" s="84"/>
+      <c r="G67" s="84"/>
+      <c r="H67" s="84"/>
+      <c r="I67" s="84"/>
+    </row>
+    <row r="68" spans="3:12">
+      <c r="C68" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D68" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="E68" s="82" t="s">
+        <v>203</v>
+      </c>
+      <c r="F68" s="83"/>
+      <c r="G68" s="83"/>
+      <c r="H68" s="83"/>
+      <c r="I68" s="83"/>
+    </row>
+    <row r="69" spans="3:12">
+      <c r="C69" s="80"/>
+      <c r="D69" s="81"/>
+      <c r="E69" s="88" t="s">
+        <v>224</v>
+      </c>
+      <c r="F69" s="89"/>
+      <c r="G69" s="89"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="90"/>
+    </row>
+    <row r="70" spans="3:12">
+      <c r="C70" s="75" t="s">
+        <v>128</v>
+      </c>
+      <c r="D70" s="76"/>
+      <c r="E70" s="91" t="s">
+        <v>221</v>
+      </c>
+      <c r="F70" s="92"/>
+      <c r="G70" s="92"/>
+      <c r="H70" s="92"/>
+      <c r="I70" s="93"/>
+    </row>
+    <row r="71" spans="3:12">
+      <c r="C71" s="16">
+        <v>80</v>
+      </c>
+      <c r="D71" s="17">
+        <v>80</v>
+      </c>
+      <c r="E71" s="86" t="s">
+        <v>222</v>
+      </c>
+      <c r="F71" s="86"/>
+      <c r="G71" s="86"/>
+      <c r="H71" s="86"/>
+      <c r="I71" s="86"/>
+    </row>
+    <row r="72" spans="3:12">
+      <c r="C72" s="16">
+        <v>90</v>
+      </c>
+      <c r="D72" s="17">
+        <v>90</v>
+      </c>
+      <c r="E72" s="87"/>
+      <c r="F72" s="87"/>
+      <c r="G72" s="87"/>
+      <c r="H72" s="87"/>
+      <c r="I72" s="87"/>
+    </row>
+    <row r="73" spans="3:12">
+      <c r="C73" s="16">
+        <v>100</v>
+      </c>
+      <c r="D73" s="17">
+        <v>100</v>
+      </c>
+      <c r="E73" s="87"/>
+      <c r="F73" s="87"/>
+      <c r="G73" s="87"/>
+      <c r="H73" s="87"/>
+      <c r="I73" s="87"/>
+    </row>
+    <row r="74" spans="3:12">
+      <c r="C74" s="16">
+        <v>100</v>
+      </c>
+      <c r="D74" s="17">
+        <v>140</v>
+      </c>
+      <c r="E74" s="87"/>
+      <c r="F74" s="87"/>
+      <c r="G74" s="87"/>
+      <c r="H74" s="87"/>
+      <c r="I74" s="87"/>
+    </row>
+    <row r="75" spans="3:12">
+      <c r="C75" s="16">
+        <v>150</v>
+      </c>
+      <c r="D75" s="17">
+        <v>150</v>
+      </c>
+      <c r="E75" s="87"/>
+      <c r="F75" s="87"/>
+      <c r="G75" s="87"/>
+      <c r="H75" s="87"/>
+      <c r="I75" s="87"/>
+    </row>
+    <row r="76" spans="3:12">
+      <c r="C76" s="16">
+        <v>150</v>
+      </c>
+      <c r="D76" s="17">
+        <v>200</v>
+      </c>
+      <c r="E76" s="87"/>
+      <c r="F76" s="87"/>
+      <c r="G76" s="87"/>
+      <c r="H76" s="87"/>
+      <c r="I76" s="87"/>
+    </row>
+    <row r="77" spans="3:12">
+      <c r="C77" s="16">
+        <v>200</v>
+      </c>
+      <c r="D77" s="17">
+        <v>200</v>
+      </c>
+      <c r="E77" s="87"/>
+      <c r="F77" s="87"/>
+      <c r="G77" s="87"/>
+      <c r="H77" s="87"/>
+      <c r="I77" s="87"/>
+    </row>
+    <row r="79" spans="3:12">
+      <c r="L79" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="48">
+    <mergeCell ref="E71:I77"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E70:I70"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="C12:I12"/>
@@ -5249,7 +5473,7 @@
     <mergeCell ref="H54:I54"/>
     <mergeCell ref="C50:I50"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -5266,128 +5490,128 @@
   </cols>
   <sheetData>
     <row r="4" spans="6:12" ht="15">
-      <c r="F4" s="69" t="s">
-        <v>224</v>
-      </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="F4" s="70" t="s">
+        <v>225</v>
+      </c>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
     </row>
     <row r="5" spans="6:12" ht="14.5" customHeight="1">
-      <c r="F5" s="86" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="H5" s="76" t="s">
-        <v>174</v>
-      </c>
-      <c r="I5" s="76"/>
-      <c r="J5" s="76"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="76"/>
+      <c r="F5" s="96" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="98" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="77" t="s">
+        <v>167</v>
+      </c>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
     </row>
     <row r="6" spans="6:12" ht="15" customHeight="1">
-      <c r="F6" s="87"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="77"/>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="6:12">
       <c r="F7" s="18">
         <v>9</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="H7" s="85">
+        <v>168</v>
+      </c>
+      <c r="H7" s="95">
         <v>700</v>
       </c>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="6:12">
       <c r="F8" s="18">
         <v>12</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="H8" s="85">
+        <v>168</v>
+      </c>
+      <c r="H8" s="95">
         <v>800</v>
       </c>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="6:12">
       <c r="F9" s="18">
         <v>15</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" s="85">
+        <v>168</v>
+      </c>
+      <c r="H9" s="95">
         <v>1100</v>
       </c>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="6:12">
       <c r="F10" s="18">
         <v>18</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="85">
+        <v>168</v>
+      </c>
+      <c r="H10" s="95">
         <v>1350</v>
       </c>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="78"/>
+      <c r="K10" s="78"/>
+      <c r="L10" s="78"/>
     </row>
     <row r="11" spans="6:12">
       <c r="F11" s="18">
         <v>22</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="85">
+        <v>168</v>
+      </c>
+      <c r="H11" s="95">
         <v>1600</v>
       </c>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="77"/>
+      <c r="I11" s="78"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="H10:L10"/>
+    <mergeCell ref="H11:L11"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:L6"/>
     <mergeCell ref="H7:L7"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="H9:L9"/>
-    <mergeCell ref="H10:L10"/>
-    <mergeCell ref="H11:L11"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>